--- a/evaluation/det_gpt_pet.xlsx
+++ b/evaluation/det_gpt_pet.xlsx
@@ -333,7 +333,7 @@
     <col width="8.8" min="1" max="1" bestFit="1" customWidth="1"/>
     <col width="5.5" min="2" max="2" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="3" max="3" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="4" max="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -349,7 +349,7 @@
         <v>0.45</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.11918726434855466</v>
+        <v>0.4663732931912265</v>
       </c>
     </row>
     <row r="2">
@@ -365,7 +365,7 @@
         <v>1.0</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.3</v>
+        <v>0.6125</v>
       </c>
     </row>
     <row r="3">
@@ -429,7 +429,7 @@
         <v>1.0</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8055555555555556</v>
       </c>
     </row>
     <row r="7">
@@ -525,7 +525,7 @@
         <v>1.0</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="13">
@@ -637,7 +637,7 @@
         <v>1.0</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>0.9857831239020144</v>
+        <v>0.9928915619510073</v>
       </c>
     </row>
     <row r="20">
@@ -653,7 +653,7 @@
         <v>0.7381396956501155</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>0.24946831773241573</v>
+        <v>0.6142078430767342</v>
       </c>
     </row>
     <row r="21">
@@ -701,7 +701,7 @@
         <v>1.0</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8133333333333332</v>
       </c>
     </row>
     <row r="24">
@@ -829,7 +829,7 @@
         <v>0.6794231121910129</v>
       </c>
       <c r="D31" s="0" t="n">
-        <v>0.5761072261072262</v>
+        <v>0.7880536130536131</v>
       </c>
     </row>
     <row r="32">
@@ -845,7 +845,7 @@
         <v>0.7857142857142857</v>
       </c>
       <c r="D32" s="0" t="n">
-        <v>0.36666666666666664</v>
+        <v>0.5849726775956284</v>
       </c>
     </row>
     <row r="33">
@@ -861,7 +861,7 @@
         <v>0.41061349582177015</v>
       </c>
       <c r="D33" s="0" t="n">
-        <v>0.41725533596837944</v>
+        <v>0.5798851530141299</v>
       </c>
     </row>
     <row r="34">
@@ -909,7 +909,7 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="D36" s="0" t="n">
-        <v>0.37777777777777777</v>
+        <v>0.6412698412698412</v>
       </c>
     </row>
     <row r="37">
@@ -925,7 +925,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="D37" s="0" t="n">
-        <v>0.5</v>
+        <v>0.6617647058823529</v>
       </c>
     </row>
     <row r="38">
@@ -977,7 +977,7 @@
         <v>0.6328186152615742</v>
       </c>
       <c r="D40" s="0" t="n">
-        <v>0.25416666666666665</v>
+        <v>0.5625672043010752</v>
       </c>
     </row>
     <row r="41">
@@ -993,7 +993,7 @@
         <v>1.0</v>
       </c>
       <c r="D41" s="0" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.7029914529914529</v>
       </c>
     </row>
     <row r="42">
@@ -1009,7 +1009,7 @@
         <v>0.7</v>
       </c>
       <c r="D42" s="0" t="n">
-        <v>0.8928571428571428</v>
+        <v>0.9464285714285714</v>
       </c>
     </row>
     <row r="43">
@@ -1057,7 +1057,7 @@
         <v>1.0</v>
       </c>
       <c r="D45" s="0" t="n">
-        <v>0.763265306122449</v>
+        <v>0.8306122448979592</v>
       </c>
     </row>
   </sheetData>

--- a/evaluation/det_gpt_pet.xlsx
+++ b/evaluation/det_gpt_pet.xlsx
@@ -333,7 +333,7 @@
     <col width="8.8" min="1" max="1" bestFit="1" customWidth="1"/>
     <col width="5.5" min="2" max="2" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="3" max="3" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="4" max="4" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -349,7 +349,7 @@
         <v>0.45</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.4663732931912265</v>
+        <v>0.09696590997848516</v>
       </c>
     </row>
     <row r="2">
@@ -365,7 +365,7 @@
         <v>1.0</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.6125</v>
+        <v>0.2775</v>
       </c>
     </row>
     <row r="3">
@@ -429,7 +429,7 @@
         <v>1.0</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.6296296296296295</v>
       </c>
     </row>
     <row r="7">
@@ -525,7 +525,7 @@
         <v>1.0</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.7777777777777778</v>
       </c>
     </row>
     <row r="13">
@@ -637,7 +637,7 @@
         <v>1.0</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>0.9928915619510073</v>
+        <v>0.9857831239020144</v>
       </c>
     </row>
     <row r="20">
@@ -653,7 +653,7 @@
         <v>0.7381396956501155</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>0.6142078430767342</v>
+        <v>0.24421635314857543</v>
       </c>
     </row>
     <row r="21">
@@ -701,7 +701,7 @@
         <v>1.0</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>0.8133333333333332</v>
+        <v>0.6399999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -829,7 +829,7 @@
         <v>0.6794231121910129</v>
       </c>
       <c r="D31" s="0" t="n">
-        <v>0.7880536130536131</v>
+        <v>0.5761072261072262</v>
       </c>
     </row>
     <row r="32">
@@ -845,7 +845,7 @@
         <v>0.7857142857142857</v>
       </c>
       <c r="D32" s="0" t="n">
-        <v>0.5849726775956284</v>
+        <v>0.29453551912568304</v>
       </c>
     </row>
     <row r="33">
@@ -861,7 +861,7 @@
         <v>0.41061349582177015</v>
       </c>
       <c r="D33" s="0" t="n">
-        <v>0.5798851530141299</v>
+        <v>0.3098183332938866</v>
       </c>
     </row>
     <row r="34">
@@ -909,7 +909,7 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="D36" s="0" t="n">
-        <v>0.6412698412698412</v>
+        <v>0.34179894179894177</v>
       </c>
     </row>
     <row r="37">
@@ -925,7 +925,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="D37" s="0" t="n">
-        <v>0.6617647058823529</v>
+        <v>0.4117647058823529</v>
       </c>
     </row>
     <row r="38">
@@ -977,7 +977,7 @@
         <v>0.6328186152615742</v>
       </c>
       <c r="D40" s="0" t="n">
-        <v>0.5625672043010752</v>
+        <v>0.22137096774193546</v>
       </c>
     </row>
     <row r="41">
@@ -993,7 +993,7 @@
         <v>1.0</v>
       </c>
       <c r="D41" s="0" t="n">
-        <v>0.7029914529914529</v>
+        <v>0.42735042735042733</v>
       </c>
     </row>
     <row r="42">
@@ -1009,7 +1009,7 @@
         <v>0.7</v>
       </c>
       <c r="D42" s="0" t="n">
-        <v>0.9464285714285714</v>
+        <v>0.8928571428571428</v>
       </c>
     </row>
     <row r="43">
@@ -1057,7 +1057,7 @@
         <v>1.0</v>
       </c>
       <c r="D45" s="0" t="n">
-        <v>0.8306122448979592</v>
+        <v>0.6853810912119951</v>
       </c>
     </row>
   </sheetData>
